--- a/output/roomself_excel/9231.xlsx
+++ b/output/roomself_excel/9231.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>214801</v>
+        <v>47189</v>
       </c>
       <c r="D2" t="n">
-        <v>4456</v>
+        <v>1796</v>
       </c>
       <c r="E2" t="n">
-        <v>825</v>
+        <v>398</v>
       </c>
       <c r="F2" t="n">
-        <v>398</v>
+        <v>281</v>
       </c>
     </row>
     <row r="3">
@@ -502,6 +502,50 @@
       </c>
       <c r="F3" t="n">
         <v>187</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Hallway</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>40271</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1668</v>
+      </c>
+      <c r="E4" t="n">
+        <v>398</v>
+      </c>
+      <c r="F4" t="n">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>127341</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3380</v>
+      </c>
+      <c r="E5" t="n">
+        <v>825</v>
+      </c>
+      <c r="F5" t="n">
+        <v>398</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/9231.xlsx
+++ b/output/roomself_excel/9231.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,47 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
         </is>
       </c>
     </row>
@@ -475,12 +510,23 @@
       <c r="D2" t="n">
         <v>1796</v>
       </c>
-      <c r="E2" t="n">
-        <v>398</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F2" t="n">
         <v>281</v>
       </c>
+      <c r="G2" t="n">
+        <v>31</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +543,31 @@
       <c r="D3" t="n">
         <v>1468</v>
       </c>
-      <c r="E3" t="n">
-        <v>279</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>187</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="G3" t="n">
+        <v>38</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>148</v>
+      </c>
+      <c r="J3" t="n">
+        <v>61</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +584,31 @@
       <c r="D4" t="n">
         <v>1668</v>
       </c>
-      <c r="E4" t="n">
-        <v>398</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>271</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="G4" t="n">
+        <v>31</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>168</v>
+      </c>
+      <c r="J4" t="n">
+        <v>33</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,11 +625,38 @@
       <c r="D5" t="n">
         <v>3380</v>
       </c>
-      <c r="E5" t="n">
-        <v>825</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>398</v>
+        <v>327</v>
+      </c>
+      <c r="G5" t="n">
+        <v>28</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>506</v>
+      </c>
+      <c r="J5" t="n">
+        <v>29</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>245</v>
+      </c>
+      <c r="M5" t="n">
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/9231.xlsx
+++ b/output/roomself_excel/9231.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rooms" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:U5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,6 +492,46 @@
       <c r="M1" s="1" t="inlineStr">
         <is>
           <t>ExtWallWidth_3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_1</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_1</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_1</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_1</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_2</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_2</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_2</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_2</t>
         </is>
       </c>
     </row>
@@ -527,6 +567,14 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -568,6 +616,14 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -609,6 +665,26 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>91</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>33</v>
+      </c>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -657,6 +733,38 @@
       </c>
       <c r="M5" t="n">
         <v>31</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>105</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>28</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="T5" t="n">
+        <v>93</v>
+      </c>
+      <c r="U5" t="n">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
